--- a/public/template/import_siswa_valid.xlsx
+++ b/public/template/import_siswa_valid.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preda\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\program_job\Laravel\Waspas_siswa\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E8FBDB-8D83-4586-9B8F-6B39EB713F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99120718-EA1E-4966-A445-CC1AB4F9D15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>nisn</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>Sari Wulandari</t>
+  </si>
+  <si>
+    <t>tahun_ajaran</t>
   </si>
 </sst>
 </file>
@@ -126,11 +129,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,16 +439,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="42.36328125" customWidth="1"/>
     <col min="6" max="6" width="51.6328125" customWidth="1"/>
     <col min="7" max="7" width="55.7265625" customWidth="1"/>
     <col min="8" max="8" width="23.54296875" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,8 +474,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1000000001</v>
       </c>
@@ -495,8 +503,11 @@
       <c r="H2">
         <v>4.7</v>
       </c>
+      <c r="I2">
+        <v>2025</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1000000002</v>
       </c>
@@ -521,8 +532,11 @@
       <c r="H3">
         <v>4.3</v>
       </c>
+      <c r="I3">
+        <v>2025</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1000000003</v>
       </c>
@@ -547,8 +561,11 @@
       <c r="H4">
         <v>3.9</v>
       </c>
+      <c r="I4">
+        <v>2025</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1000000004</v>
       </c>
@@ -573,8 +590,11 @@
       <c r="H5">
         <v>4.9000000000000004</v>
       </c>
+      <c r="I5">
+        <v>2025</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1000000005</v>
       </c>
@@ -598,6 +618,9 @@
       </c>
       <c r="H6">
         <v>4.0999999999999996</v>
+      </c>
+      <c r="I6">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>

--- a/public/template/import_siswa_valid.xlsx
+++ b/public/template/import_siswa_valid.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\program_job\Laravel\Waspas_siswa\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99120718-EA1E-4966-A445-CC1AB4F9D15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C523CB9-0845-4C18-9B17-88AC75BBD6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="2240" windowWidth="19200" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>nisn</t>
   </si>
@@ -31,19 +31,40 @@
     <t>jenis_kelamin</t>
   </si>
   <si>
+    <t>asal_kelas</t>
+  </si>
+  <si>
     <t>jurusan</t>
   </si>
   <si>
+    <t>tahun_ajaran</t>
+  </si>
+  <si>
+    <t>tes_wawancara</t>
+  </si>
+  <si>
+    <t>tes_tulis</t>
+  </si>
+  <si>
+    <t>tes_hafalan_quran</t>
+  </si>
+  <si>
     <t>nilai_rapor</t>
   </si>
   <si>
-    <t>prestasi_akademik</t>
-  </si>
-  <si>
-    <t>prestasi_non_akademik</t>
-  </si>
-  <si>
-    <t>kedisiplinan</t>
+    <t>prestasi</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>0987654321</t>
+  </si>
+  <si>
+    <t>Ahmad Rafi</t>
+  </si>
+  <si>
+    <t>Siti Zahra</t>
   </si>
   <si>
     <t>Laki-laki</t>
@@ -52,25 +73,16 @@
     <t>Perempuan</t>
   </si>
   <si>
-    <t>12TKJ</t>
-  </si>
-  <si>
-    <t>Ahmad Fadli</t>
-  </si>
-  <si>
-    <t>Nur Aisyah</t>
-  </si>
-  <si>
-    <t>Bagus Pratama</t>
-  </si>
-  <si>
-    <t>Lia Melati</t>
-  </si>
-  <si>
-    <t>Sari Wulandari</t>
-  </si>
-  <si>
-    <t>tahun_ajaran</t>
+    <t>9A</t>
+  </si>
+  <si>
+    <t>9B</t>
+  </si>
+  <si>
+    <t>Teknik Komputer</t>
+  </si>
+  <si>
+    <t>Akuntansi</t>
   </si>
 </sst>
 </file>
@@ -129,12 +141,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,17 +450,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="42.36328125" customWidth="1"/>
-    <col min="6" max="6" width="51.6328125" customWidth="1"/>
-    <col min="7" max="7" width="55.7265625" customWidth="1"/>
-    <col min="8" max="8" width="23.54296875" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" customWidth="1"/>
+    <col min="1" max="1" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="27.08984375" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="31.54296875" customWidth="1"/>
+    <col min="7" max="7" width="28.6328125" customWidth="1"/>
+    <col min="8" max="9" width="20.36328125" customWidth="1"/>
+    <col min="10" max="10" width="28.36328125" customWidth="1"/>
+    <col min="11" max="11" width="29.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,153 +489,84 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>2025</v>
+      </c>
+      <c r="G2">
+        <v>85</v>
+      </c>
+      <c r="H2">
+        <v>78</v>
+      </c>
+      <c r="I2">
+        <v>90</v>
+      </c>
+      <c r="J2">
+        <v>88</v>
+      </c>
+      <c r="K2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1000000001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>4.5</v>
-      </c>
-      <c r="F2">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G2">
-        <v>3.9</v>
-      </c>
-      <c r="H2">
-        <v>4.7</v>
-      </c>
-      <c r="I2">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1000000002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>4.2</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>70</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>82</v>
       </c>
       <c r="I3">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>1000000003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>3.9</v>
-      </c>
-      <c r="F4">
-        <v>3.6</v>
-      </c>
-      <c r="G4">
-        <v>2.8</v>
-      </c>
-      <c r="H4">
-        <v>3.9</v>
-      </c>
-      <c r="I4">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1000000004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5">
-        <v>4.8</v>
-      </c>
-      <c r="F5">
-        <v>4.7</v>
-      </c>
-      <c r="G5">
-        <v>4.5</v>
-      </c>
-      <c r="H5">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="I5">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1000000005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3.8</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="I6">
-        <v>2025</v>
+        <v>60</v>
+      </c>
+      <c r="J3">
+        <v>85</v>
+      </c>
+      <c r="K3">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
